--- a/LLM_/My side/Test casses.xlsx
+++ b/LLM_/My side/Test casses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karan\Desktop\TK\TK\LLM_\My side\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8DBB93-172A-439F-ADBB-4EA44A1738F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396A6783-2B88-439A-B8BE-575D550D3161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F3D031E3-95AB-4794-8ED5-3508E76B7363}"/>
   </bookViews>
@@ -823,12 +823,18 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -843,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -855,6 +861,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1281,19 +1296,19 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="33" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="7" t="s">
         <v>34</v>
       </c>
     </row>
